--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEW_MEXICO_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/NEW_MEXICO_2010.xlsx
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C128">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C175">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C209">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C587">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="B913" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C913">
